--- a/tte/demo/tte_report_pp.xlsx
+++ b/tte/demo/tte_report_pp.xlsx
@@ -164,28 +164,859 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="5">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
+  <fonts count="203">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -196,7 +1027,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="120">
     <border>
       <left/>
       <right/>
@@ -220,11 +1051,804 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -233,6 +1857,460 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="19" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="22" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="23" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="24" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="25" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="26" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="27" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="28" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="29" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="30" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="31" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="32" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="35" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="36" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="37" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="38" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="39" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="40" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="41" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="42" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="43" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="45" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="46" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="47" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="48" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="50" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="51" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="52" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="53" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="54" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="55" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="56" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="57" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="58" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="59" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="60" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="61" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="62" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="63" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="64" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="65" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="66" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="67" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="68" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="69" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="70" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="71" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="72" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="73" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="74" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="75" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="76" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="77" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="78" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="79" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="80" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="0" borderId="81" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="82" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="83" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="0" borderId="84" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="85" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="86" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="87" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="88" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="142" fillId="0" borderId="89" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="144" fillId="0" borderId="90" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="91" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="148" fillId="0" borderId="92" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="150" fillId="0" borderId="93" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="152" fillId="0" borderId="94" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="154" fillId="0" borderId="95" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="156" fillId="0" borderId="96" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="158" fillId="0" borderId="97" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="160" fillId="0" borderId="98" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="162" fillId="0" borderId="99" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="164" fillId="0" borderId="100" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="166" fillId="0" borderId="101" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="168" fillId="0" borderId="102" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="170" fillId="0" borderId="103" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="172" fillId="0" borderId="104" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="174" fillId="0" borderId="105" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="176" fillId="0" borderId="106" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="178" fillId="0" borderId="107" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="180" fillId="0" borderId="108" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="182" fillId="0" borderId="109" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="184" fillId="0" borderId="110" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="186" fillId="0" borderId="111" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="188" fillId="0" borderId="112" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="190" fillId="0" borderId="113" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="192" fillId="0" borderId="114" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="194" fillId="0" borderId="115" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="196" fillId="0" borderId="116" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="198" fillId="0" borderId="117" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="200" fillId="0" borderId="118" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="202" fillId="0" borderId="119" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -253,64 +2331,68 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
+      <c r="B1" s="16"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="17"/>
+      <c r="B2" s="18"/>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="20" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="22" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
+      <c r="A5" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="24">
         <v>998110</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s">
+      <c r="A6" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="26">
         <v>116947</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s">
+      <c r="A7" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="28">
         <v>881163</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="s">
+      <c r="A8" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="30">
         <v>4082</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="s">
+      <c r="A9" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="32">
         <v>396</v>
       </c>
     </row>
@@ -325,208 +2407,212 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22.7109375" style="33" customWidth="true"/>
+    <col min="2" max="5" width="14.7109375" style="34" customWidth="true"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="64" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" s="65" t="s">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="69" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" s="70" t="s">
         <v>19</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="74" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="79" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
+      <c r="A5" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="82" t="s">
         <v>17</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="83" t="s">
         <v>17</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="84" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s">
+      <c r="A6" s="85" t="s">
         <v>28</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="86" t="s">
         <v>29</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="87" t="s">
         <v>17</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="89" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s">
+      <c r="A7" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="91" t="s">
         <v>32</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="92" t="s">
         <v>17</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="93" t="s">
         <v>17</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="94" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="s">
+      <c r="A8" s="95" t="s">
         <v>34</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="96" t="s">
         <v>35</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="97" t="s">
         <v>17</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="98" t="s">
         <v>17</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="99" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="s">
+      <c r="A9" s="100" t="s">
         <v>37</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="101" t="s">
         <v>38</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="102" t="s">
         <v>17</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="103" t="s">
         <v>17</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="104" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="s">
+      <c r="A10" s="105" t="s">
         <v>40</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="107" t="s">
         <v>17</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="108" t="s">
         <v>17</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="109" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s">
+      <c r="A11" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="111" t="s">
         <v>44</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="112" t="s">
         <v>17</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="113" t="s">
         <v>17</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="114" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s">
+      <c r="A12" s="115" t="s">
         <v>46</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="116" t="s">
         <v>47</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="117" t="s">
         <v>17</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="118" t="s">
         <v>17</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="119" t="s">
         <v>29</v>
       </c>
     </row>
